--- a/Results2ndRound/Tests2.xlsx
+++ b/Results2ndRound/Tests2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Irma1\Documents\Tesis_tests\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Irma1\Documents\Tesis_tests\Results2ndRound\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8A0C90-7AD8-45DB-962C-1A4E091856A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B04797-CDB6-4BCC-AD78-AE37359EB437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{9811F352-0CC2-49A3-8C55-61560FCE2FC5}"/>
   </bookViews>
@@ -657,6 +657,7 @@
         <v>1E-3</v>
       </c>
       <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -678,6 +679,7 @@
         <v>0.05</v>
       </c>
       <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -699,6 +701,7 @@
         <v>0.01</v>
       </c>
       <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -720,6 +723,7 @@
         <v>0.1</v>
       </c>
       <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -741,6 +745,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -762,6 +767,7 @@
         <v>1E-3</v>
       </c>
       <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -783,6 +789,7 @@
         <v>0.05</v>
       </c>
       <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -804,6 +811,7 @@
         <v>0.01</v>
       </c>
       <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -825,6 +833,7 @@
         <v>0.1</v>
       </c>
       <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -846,6 +855,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -867,6 +877,7 @@
         <v>1E-3</v>
       </c>
       <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -888,6 +899,7 @@
         <v>0.05</v>
       </c>
       <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -909,6 +921,7 @@
         <v>0.01</v>
       </c>
       <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -930,6 +943,7 @@
         <v>0.1</v>
       </c>
       <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -951,8 +965,9 @@
         <v>1</v>
       </c>
       <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -972,8 +987,9 @@
         <v>1E-3</v>
       </c>
       <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -993,8 +1009,9 @@
         <v>0.05</v>
       </c>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1014,8 +1031,9 @@
         <v>0.01</v>
       </c>
       <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1035,8 +1053,9 @@
         <v>0.1</v>
       </c>
       <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1056,8 +1075,9 @@
         <v>1</v>
       </c>
       <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1077,8 +1097,9 @@
         <v>1E-3</v>
       </c>
       <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1098,8 +1119,9 @@
         <v>0.05</v>
       </c>
       <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1119,8 +1141,9 @@
         <v>0.01</v>
       </c>
       <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1140,8 +1163,9 @@
         <v>0.1</v>
       </c>
       <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1161,8 +1185,9 @@
         <v>1</v>
       </c>
       <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1182,8 +1207,9 @@
         <v>1E-3</v>
       </c>
       <c r="G27" s="4"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1203,8 +1229,9 @@
         <v>0.05</v>
       </c>
       <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1224,8 +1251,9 @@
         <v>0.01</v>
       </c>
       <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1245,8 +1273,9 @@
         <v>0.1</v>
       </c>
       <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1266,8 +1295,9 @@
         <v>1</v>
       </c>
       <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1287,8 +1317,9 @@
         <v>1E-3</v>
       </c>
       <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1308,8 +1339,9 @@
         <v>0.05</v>
       </c>
       <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1329,8 +1361,9 @@
         <v>0.01</v>
       </c>
       <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1350,8 +1383,9 @@
         <v>0.1</v>
       </c>
       <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1371,8 +1405,9 @@
         <v>1</v>
       </c>
       <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1392,8 +1427,9 @@
         <v>1E-3</v>
       </c>
       <c r="G37" s="3"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1413,8 +1449,9 @@
         <v>0.05</v>
       </c>
       <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1434,8 +1471,9 @@
         <v>0.01</v>
       </c>
       <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1455,8 +1493,9 @@
         <v>0.1</v>
       </c>
       <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1476,8 +1515,9 @@
         <v>1</v>
       </c>
       <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1497,8 +1537,9 @@
         <v>1E-3</v>
       </c>
       <c r="G42" s="3"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1518,8 +1559,9 @@
         <v>0.05</v>
       </c>
       <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -1539,8 +1581,9 @@
         <v>0.01</v>
       </c>
       <c r="G44" s="5"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1560,8 +1603,9 @@
         <v>0.1</v>
       </c>
       <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H45" s="2"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1581,6 +1625,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Results2ndRound/Tests2.xlsx
+++ b/Results2ndRound/Tests2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Irma1\Documents\Tesis_tests\Results2ndRound\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B04797-CDB6-4BCC-AD78-AE37359EB437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D454927-54C2-42CE-8A08-1D0822A189B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{9811F352-0CC2-49A3-8C55-61560FCE2FC5}"/>
+    <workbookView xWindow="32280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9811F352-0CC2-49A3-8C55-61560FCE2FC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Prueba</t>
   </si>
@@ -195,13 +195,35 @@
   </si>
   <si>
     <t>Rust</t>
+  </si>
+  <si>
+    <t>Mosquitto Min</t>
+  </si>
+  <si>
+    <t>Mosquitto Max</t>
+  </si>
+  <si>
+    <t>Mosquitto Avg</t>
+  </si>
+  <si>
+    <t>Rust Max</t>
+  </si>
+  <si>
+    <t>Rust Min</t>
+  </si>
+  <si>
+    <t>Rust Avg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -225,6 +247,13 @@
     <font>
       <sz val="11"/>
       <color theme="5" tint="0.59999389629810485"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -259,21 +288,80 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -284,6 +372,29 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E369A01A-5455-4049-B143-B0A75EDB0056}" name="Table1" displayName="Table1" ref="A1:N46">
+  <autoFilter ref="A1:N46" xr:uid="{E369A01A-5455-4049-B143-B0A75EDB0056}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{6B8FA1ED-B126-4A31-B12B-6CA852B57F57}" name="Prueba" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{A0D00EDB-33D0-49B2-A8EC-77BB33C8C9CE}" name="Publishers"/>
+    <tableColumn id="3" xr3:uid="{6EFB38A4-2061-4BCB-BE0E-87D7D29A43D3}" name="Suscribers"/>
+    <tableColumn id="4" xr3:uid="{8B7BD022-94F8-475F-8FA7-3B0D256E8DF9}" name="Payload (Bytes)" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{167C89BD-FECF-4BFD-A97F-9EBE92CC1830}" name="Tiempo"/>
+    <tableColumn id="6" xr3:uid="{BC0FE7DC-846C-44E9-A1FA-E75C1CB6FD8C}" name="Frecuencia"/>
+    <tableColumn id="7" xr3:uid="{F340379E-B31A-452C-8EAB-8CCF3A03DB4B}" name="Mosquitto" dataDxfId="9" totalsRowDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{6E9A1A8D-39A4-49C7-AAB7-0D5FEE913168}" name="Rust" dataDxfId="6" totalsRowDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{1C5BD2CA-BF23-4EC1-BC6B-A7ADB67970E0}" name="Mosquitto Max" dataDxfId="5" dataCellStyle="Comma"/>
+    <tableColumn id="10" xr3:uid="{00835658-1C66-41FD-A11A-43E59B19EDA7}" name="Mosquitto Min" dataDxfId="4" dataCellStyle="Comma"/>
+    <tableColumn id="11" xr3:uid="{A371C36D-EE1C-4181-AB92-18FB141B0F99}" name="Mosquitto Avg" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="12" xr3:uid="{5A0130F1-71AE-41AF-B26D-F17F2B3A380C}" name="Rust Max" dataDxfId="2" dataCellStyle="Comma"/>
+    <tableColumn id="13" xr3:uid="{B2BC73AC-73AD-4C33-9D27-E8AC1FC86A08}" name="Rust Min" dataDxfId="1" dataCellStyle="Comma"/>
+    <tableColumn id="14" xr3:uid="{55C02AA7-2C33-4C83-AB47-4591B8C50557}" name="Rust Avg" totalsRowFunction="count" dataDxfId="0" dataCellStyle="Comma"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -603,15 +714,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842D6BDC-3AC3-4C20-B433-D06981D498A1}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.1796875" customWidth="1"/>
+    <col min="4" max="4" width="14.90625" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" customWidth="1"/>
+    <col min="7" max="7" width="10.81640625" customWidth="1"/>
+    <col min="9" max="9" width="14.36328125" customWidth="1"/>
+    <col min="10" max="11" width="14.08984375" customWidth="1"/>
+    <col min="12" max="12" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -636,8 +753,26 @@
       <c r="H1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -658,8 +793,26 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" s="6">
+        <v>10332</v>
+      </c>
+      <c r="J2" s="6">
+        <v>7472</v>
+      </c>
+      <c r="K2" s="6">
+        <v>9661.4375</v>
+      </c>
+      <c r="L2" s="6">
+        <v>51576</v>
+      </c>
+      <c r="M2" s="6">
+        <v>5652</v>
+      </c>
+      <c r="N2" s="6">
+        <v>41586.446279999996</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -680,8 +833,26 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" s="6">
+        <v>7852</v>
+      </c>
+      <c r="J3" s="6">
+        <v>7448</v>
+      </c>
+      <c r="K3" s="6">
+        <v>7807.069767</v>
+      </c>
+      <c r="L3" s="6">
+        <v>18384</v>
+      </c>
+      <c r="M3" s="6">
+        <v>10028</v>
+      </c>
+      <c r="N3" s="6">
+        <v>14370.12903</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -702,8 +873,26 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" s="6">
+        <v>9816</v>
+      </c>
+      <c r="J4" s="6">
+        <v>7428</v>
+      </c>
+      <c r="K4" s="6">
+        <v>9087.6581200000001</v>
+      </c>
+      <c r="L4" s="6">
+        <v>40184</v>
+      </c>
+      <c r="M4" s="6">
+        <v>5604</v>
+      </c>
+      <c r="N4" s="6">
+        <v>24536.74797</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -724,8 +913,26 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5" s="6">
+        <v>7560</v>
+      </c>
+      <c r="J5" s="6">
+        <v>7444</v>
+      </c>
+      <c r="K5" s="6">
+        <v>7537.3333329999996</v>
+      </c>
+      <c r="L5" s="6">
+        <v>11548</v>
+      </c>
+      <c r="M5" s="6">
+        <v>5624</v>
+      </c>
+      <c r="N5" s="6">
+        <v>9439.4146340000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -746,8 +953,26 @@
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6" s="6">
+        <v>7428</v>
+      </c>
+      <c r="J6" s="6">
+        <v>7384</v>
+      </c>
+      <c r="K6" s="6">
+        <v>7427.1803280000004</v>
+      </c>
+      <c r="L6" s="6">
+        <v>8072</v>
+      </c>
+      <c r="M6" s="6">
+        <v>5636</v>
+      </c>
+      <c r="N6" s="6">
+        <v>7755.9344259999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -768,8 +993,26 @@
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7" s="6">
+        <v>10888</v>
+      </c>
+      <c r="J7" s="6">
+        <v>7416</v>
+      </c>
+      <c r="K7" s="6">
+        <v>9835.7024789999996</v>
+      </c>
+      <c r="L7" s="6">
+        <v>24176</v>
+      </c>
+      <c r="M7" s="6">
+        <v>5620</v>
+      </c>
+      <c r="N7" s="6">
+        <v>22665.31148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -790,8 +1033,26 @@
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8" s="6">
+        <v>7644</v>
+      </c>
+      <c r="J8" s="6">
+        <v>7428</v>
+      </c>
+      <c r="K8" s="6">
+        <v>7636.033058</v>
+      </c>
+      <c r="L8" s="6">
+        <v>20956</v>
+      </c>
+      <c r="M8" s="6">
+        <v>5648</v>
+      </c>
+      <c r="N8" s="6">
+        <v>17441.788619999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -812,8 +1073,26 @@
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9" s="6">
+        <v>9964</v>
+      </c>
+      <c r="J9" s="6">
+        <v>7448</v>
+      </c>
+      <c r="K9" s="6">
+        <v>9773.85124</v>
+      </c>
+      <c r="L9" s="6">
+        <v>21428</v>
+      </c>
+      <c r="M9" s="6">
+        <v>5788</v>
+      </c>
+      <c r="N9" s="6">
+        <v>20207.024389999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -834,8 +1113,26 @@
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I10" s="6">
+        <v>7512</v>
+      </c>
+      <c r="J10" s="6">
+        <v>7444</v>
+      </c>
+      <c r="K10" s="6">
+        <v>7504.9836070000001</v>
+      </c>
+      <c r="L10" s="6">
+        <v>20608</v>
+      </c>
+      <c r="M10" s="6">
+        <v>5592</v>
+      </c>
+      <c r="N10" s="6">
+        <v>14674.43902</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -856,8 +1153,26 @@
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I11" s="6">
+        <v>7448</v>
+      </c>
+      <c r="J11" s="6">
+        <v>7384</v>
+      </c>
+      <c r="K11" s="6">
+        <v>7440.7804880000003</v>
+      </c>
+      <c r="L11" s="6">
+        <v>9300</v>
+      </c>
+      <c r="M11" s="6">
+        <v>5752</v>
+      </c>
+      <c r="N11" s="6">
+        <v>8428.419355</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -878,8 +1193,26 @@
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" s="6">
+        <v>53116</v>
+      </c>
+      <c r="J12" s="6">
+        <v>37848</v>
+      </c>
+      <c r="K12" s="6">
+        <v>46424.285709999996</v>
+      </c>
+      <c r="L12" s="6">
+        <v>53636</v>
+      </c>
+      <c r="M12" s="6">
+        <v>5644</v>
+      </c>
+      <c r="N12" s="6">
+        <v>42433.793100000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -900,8 +1233,26 @@
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13" s="6">
+        <v>7892</v>
+      </c>
+      <c r="J13" s="6">
+        <v>7424</v>
+      </c>
+      <c r="K13" s="6">
+        <v>7747.7</v>
+      </c>
+      <c r="L13" s="6">
+        <v>25772</v>
+      </c>
+      <c r="M13" s="6">
+        <v>5656</v>
+      </c>
+      <c r="N13" s="6">
+        <v>24777.48387</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -922,8 +1273,26 @@
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14" s="6">
+        <v>19092</v>
+      </c>
+      <c r="J14" s="6">
+        <v>7424</v>
+      </c>
+      <c r="K14" s="6">
+        <v>18595.033329999998</v>
+      </c>
+      <c r="L14" s="6">
+        <v>26640</v>
+      </c>
+      <c r="M14" s="6">
+        <v>5728</v>
+      </c>
+      <c r="N14" s="6">
+        <v>25954.959350000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -944,8 +1313,26 @@
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" s="6">
+        <v>7628</v>
+      </c>
+      <c r="J15" s="6">
+        <v>7452</v>
+      </c>
+      <c r="K15" s="6">
+        <v>7616.7272730000004</v>
+      </c>
+      <c r="L15" s="6">
+        <v>26188</v>
+      </c>
+      <c r="M15" s="6">
+        <v>5636</v>
+      </c>
+      <c r="N15" s="6">
+        <v>24876.780490000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -966,8 +1353,26 @@
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" s="6">
+        <v>7576</v>
+      </c>
+      <c r="J16" s="6">
+        <v>7428</v>
+      </c>
+      <c r="K16" s="6">
+        <v>7562.3606559999998</v>
+      </c>
+      <c r="L16" s="6">
+        <v>26184</v>
+      </c>
+      <c r="M16" s="6">
+        <v>5664</v>
+      </c>
+      <c r="N16" s="6">
+        <v>18198.622950000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -988,8 +1393,26 @@
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17" s="6">
+        <v>10672</v>
+      </c>
+      <c r="J17" s="6">
+        <v>6832</v>
+      </c>
+      <c r="K17" s="6">
+        <v>8878.7333330000001</v>
+      </c>
+      <c r="L17" s="6">
+        <v>52556</v>
+      </c>
+      <c r="M17" s="6">
+        <v>5492</v>
+      </c>
+      <c r="N17" s="6">
+        <v>46058.032789999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1010,8 +1433,26 @@
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18" s="6">
+        <v>10160</v>
+      </c>
+      <c r="J18" s="6">
+        <v>6960</v>
+      </c>
+      <c r="K18" s="6">
+        <v>10017.593500000001</v>
+      </c>
+      <c r="L18" s="6">
+        <v>29232</v>
+      </c>
+      <c r="M18" s="6">
+        <v>5648</v>
+      </c>
+      <c r="N18" s="6">
+        <v>19063.902440000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -1032,8 +1473,26 @@
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I19" s="6">
+        <v>11408</v>
+      </c>
+      <c r="J19" s="6">
+        <v>6984</v>
+      </c>
+      <c r="K19" s="6">
+        <v>10858.25726</v>
+      </c>
+      <c r="L19" s="6">
+        <v>43444</v>
+      </c>
+      <c r="M19" s="6">
+        <v>5648</v>
+      </c>
+      <c r="N19" s="6">
+        <v>35776.59016</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1054,8 +1513,26 @@
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20" s="6">
+        <v>10304</v>
+      </c>
+      <c r="J20" s="6">
+        <v>7104</v>
+      </c>
+      <c r="K20" s="6">
+        <v>10103.768599999999</v>
+      </c>
+      <c r="L20" s="6">
+        <v>19636</v>
+      </c>
+      <c r="M20" s="6">
+        <v>5640</v>
+      </c>
+      <c r="N20" s="6">
+        <v>14451.34426</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -1076,8 +1553,26 @@
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I21" s="6">
+        <v>7184</v>
+      </c>
+      <c r="J21" s="6">
+        <v>7044</v>
+      </c>
+      <c r="K21" s="6">
+        <v>7179.2131149999996</v>
+      </c>
+      <c r="L21" s="6">
+        <v>10832</v>
+      </c>
+      <c r="M21" s="6">
+        <v>5680</v>
+      </c>
+      <c r="N21" s="6">
+        <v>9997.0406500000008</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -1098,8 +1593,26 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I22" s="6">
+        <v>13888</v>
+      </c>
+      <c r="J22" s="6">
+        <v>7112</v>
+      </c>
+      <c r="K22" s="6">
+        <v>13495.404259999999</v>
+      </c>
+      <c r="L22" s="6">
+        <v>31692</v>
+      </c>
+      <c r="M22" s="6">
+        <v>5640</v>
+      </c>
+      <c r="N22" s="6">
+        <v>30577.728810000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1120,8 +1633,26 @@
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I23" s="6">
+        <v>11288</v>
+      </c>
+      <c r="J23" s="6">
+        <v>7128</v>
+      </c>
+      <c r="K23" s="6">
+        <v>11087.772360000001</v>
+      </c>
+      <c r="L23" s="6">
+        <v>25252</v>
+      </c>
+      <c r="M23" s="6">
+        <v>5748</v>
+      </c>
+      <c r="N23" s="6">
+        <v>22060.3871</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1142,8 +1673,26 @@
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I24" s="6">
+        <v>13732</v>
+      </c>
+      <c r="J24" s="6">
+        <v>7108</v>
+      </c>
+      <c r="K24" s="6">
+        <v>13326.5124</v>
+      </c>
+      <c r="L24" s="6">
+        <v>26548</v>
+      </c>
+      <c r="M24" s="6">
+        <v>5556</v>
+      </c>
+      <c r="N24" s="6">
+        <v>25229.593499999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1164,8 +1713,26 @@
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I25" s="6">
+        <v>11388</v>
+      </c>
+      <c r="J25" s="6">
+        <v>7100</v>
+      </c>
+      <c r="K25" s="6">
+        <v>11112.09677</v>
+      </c>
+      <c r="L25" s="6">
+        <v>23468</v>
+      </c>
+      <c r="M25" s="6">
+        <v>5640</v>
+      </c>
+      <c r="N25" s="6">
+        <v>20270.983609999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -1186,8 +1753,26 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I26" s="6">
+        <v>7336</v>
+      </c>
+      <c r="J26" s="6">
+        <v>7056</v>
+      </c>
+      <c r="K26" s="6">
+        <v>7289.741935</v>
+      </c>
+      <c r="L26" s="6">
+        <v>14048</v>
+      </c>
+      <c r="M26" s="6">
+        <v>5752</v>
+      </c>
+      <c r="N26" s="6">
+        <v>11607.934429999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1208,8 +1793,20 @@
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="6">
+        <v>72736</v>
+      </c>
+      <c r="M27" s="6">
+        <v>5672</v>
+      </c>
+      <c r="N27" s="6">
+        <v>67337.137929999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1230,8 +1827,26 @@
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I28" s="6">
+        <v>20964</v>
+      </c>
+      <c r="J28" s="6">
+        <v>7452</v>
+      </c>
+      <c r="K28" s="6">
+        <v>20333.934430000001</v>
+      </c>
+      <c r="L28" s="6">
+        <v>37088</v>
+      </c>
+      <c r="M28" s="6">
+        <v>5624</v>
+      </c>
+      <c r="N28" s="6">
+        <v>31373.203249999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1252,8 +1867,26 @@
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I29" s="6">
+        <v>21040</v>
+      </c>
+      <c r="J29" s="6">
+        <v>7364</v>
+      </c>
+      <c r="K29" s="6">
+        <v>20270.710739999999</v>
+      </c>
+      <c r="L29" s="6">
+        <v>70624</v>
+      </c>
+      <c r="M29" s="6">
+        <v>5488</v>
+      </c>
+      <c r="N29" s="6">
+        <v>62846.053099999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1274,8 +1907,26 @@
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I30" s="6">
+        <v>20912</v>
+      </c>
+      <c r="J30" s="6">
+        <v>7416</v>
+      </c>
+      <c r="K30" s="6">
+        <v>19845.4876</v>
+      </c>
+      <c r="L30" s="6">
+        <v>32836</v>
+      </c>
+      <c r="M30" s="6">
+        <v>5620</v>
+      </c>
+      <c r="N30" s="6">
+        <v>30396.819670000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1296,8 +1947,26 @@
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I31" s="6">
+        <v>7896</v>
+      </c>
+      <c r="J31" s="6">
+        <v>7436</v>
+      </c>
+      <c r="K31" s="6">
+        <v>7842.7967479999998</v>
+      </c>
+      <c r="L31" s="6">
+        <v>33388</v>
+      </c>
+      <c r="M31" s="6">
+        <v>5712</v>
+      </c>
+      <c r="N31" s="6">
+        <v>27591.317070000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1318,8 +1987,26 @@
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I32" s="6">
+        <v>13700</v>
+      </c>
+      <c r="J32" s="6">
+        <v>7352</v>
+      </c>
+      <c r="K32" s="6">
+        <v>13400.721310000001</v>
+      </c>
+      <c r="L32" s="6">
+        <v>61956</v>
+      </c>
+      <c r="M32" s="6">
+        <v>5608</v>
+      </c>
+      <c r="N32" s="6">
+        <v>57568.918030000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1340,8 +2027,26 @@
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I33" s="6">
+        <v>13692</v>
+      </c>
+      <c r="J33" s="6">
+        <v>7412</v>
+      </c>
+      <c r="K33" s="6">
+        <v>13457.19008</v>
+      </c>
+      <c r="L33" s="6">
+        <v>46604</v>
+      </c>
+      <c r="M33" s="6">
+        <v>5640</v>
+      </c>
+      <c r="N33" s="6">
+        <v>31520.229510000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1362,8 +2067,26 @@
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I34" s="6">
+        <v>14060</v>
+      </c>
+      <c r="J34" s="6">
+        <v>7424</v>
+      </c>
+      <c r="K34" s="6">
+        <v>13737.85124</v>
+      </c>
+      <c r="L34" s="6">
+        <v>52568</v>
+      </c>
+      <c r="M34" s="6">
+        <v>5672</v>
+      </c>
+      <c r="N34" s="6">
+        <v>47722</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -1384,8 +2107,26 @@
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I35" s="6">
+        <v>13748</v>
+      </c>
+      <c r="J35" s="6">
+        <v>7432</v>
+      </c>
+      <c r="K35" s="6">
+        <v>13460.82645</v>
+      </c>
+      <c r="L35" s="6">
+        <v>32856</v>
+      </c>
+      <c r="M35" s="6">
+        <v>5848</v>
+      </c>
+      <c r="N35" s="6">
+        <v>22382.459019999998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -1406,8 +2147,26 @@
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I36" s="6">
+        <v>7972</v>
+      </c>
+      <c r="J36" s="6">
+        <v>7452</v>
+      </c>
+      <c r="K36" s="6">
+        <v>7902.2764230000002</v>
+      </c>
+      <c r="L36" s="6">
+        <v>14900</v>
+      </c>
+      <c r="M36" s="6">
+        <v>5472</v>
+      </c>
+      <c r="N36" s="6">
+        <v>13509.54098</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1428,8 +2187,20 @@
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="2"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="6">
+        <v>46928</v>
+      </c>
+      <c r="M37" s="6">
+        <v>5632</v>
+      </c>
+      <c r="N37" s="6">
+        <v>44379.527430000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -1450,8 +2221,26 @@
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I38" s="6">
+        <v>14848</v>
+      </c>
+      <c r="J38" s="6">
+        <v>7288</v>
+      </c>
+      <c r="K38" s="6">
+        <v>14246.44015</v>
+      </c>
+      <c r="L38" s="6">
+        <v>36568</v>
+      </c>
+      <c r="M38" s="6">
+        <v>5680</v>
+      </c>
+      <c r="N38" s="6">
+        <v>29861.19457</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -1472,8 +2261,26 @@
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I39" s="6">
+        <v>16060</v>
+      </c>
+      <c r="J39" s="6">
+        <v>7436</v>
+      </c>
+      <c r="K39" s="6">
+        <v>14980.62551</v>
+      </c>
+      <c r="L39" s="6">
+        <v>37520</v>
+      </c>
+      <c r="M39" s="6">
+        <v>5732</v>
+      </c>
+      <c r="N39" s="6">
+        <v>36233.049180000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -1494,8 +2301,26 @@
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I40" s="6">
+        <v>14548</v>
+      </c>
+      <c r="J40" s="6">
+        <v>7440</v>
+      </c>
+      <c r="K40" s="6">
+        <v>14238.049590000001</v>
+      </c>
+      <c r="L40" s="6">
+        <v>29244</v>
+      </c>
+      <c r="M40" s="6">
+        <v>5596</v>
+      </c>
+      <c r="N40" s="6">
+        <v>26729.040649999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -1516,8 +2341,26 @@
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I41" s="6">
+        <v>8032</v>
+      </c>
+      <c r="J41" s="6">
+        <v>7408</v>
+      </c>
+      <c r="K41" s="6">
+        <v>8000.2622950000004</v>
+      </c>
+      <c r="L41" s="6">
+        <v>20368</v>
+      </c>
+      <c r="M41" s="6">
+        <v>5548</v>
+      </c>
+      <c r="N41" s="6">
+        <v>16138.47934</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -1538,8 +2381,20 @@
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="2"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="6">
+        <v>115612</v>
+      </c>
+      <c r="M42" s="6">
+        <v>5536</v>
+      </c>
+      <c r="N42" s="6">
+        <v>103457.34480000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -1560,8 +2415,26 @@
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I43" s="6">
+        <v>23596</v>
+      </c>
+      <c r="J43" s="6">
+        <v>7368</v>
+      </c>
+      <c r="K43" s="6">
+        <v>22971.801650000001</v>
+      </c>
+      <c r="L43" s="6">
+        <v>91140</v>
+      </c>
+      <c r="M43" s="6">
+        <v>5648</v>
+      </c>
+      <c r="N43" s="6">
+        <v>85932.392860000007</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -1582,8 +2455,20 @@
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="2"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="6">
+        <v>106112</v>
+      </c>
+      <c r="M44" s="6">
+        <v>5744</v>
+      </c>
+      <c r="N44" s="6">
+        <v>96311.620689999996</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -1604,8 +2489,26 @@
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I45" s="6">
+        <v>23632</v>
+      </c>
+      <c r="J45" s="6">
+        <v>7348</v>
+      </c>
+      <c r="K45" s="6">
+        <v>22794.876029999999</v>
+      </c>
+      <c r="L45" s="6">
+        <v>70264</v>
+      </c>
+      <c r="M45" s="6">
+        <v>5456</v>
+      </c>
+      <c r="N45" s="6">
+        <v>57912</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -1626,9 +2529,30 @@
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
+      <c r="I46" s="6">
+        <v>8504</v>
+      </c>
+      <c r="J46" s="6">
+        <v>7372</v>
+      </c>
+      <c r="K46" s="6">
+        <v>8389.8536590000003</v>
+      </c>
+      <c r="L46" s="6">
+        <v>37648</v>
+      </c>
+      <c r="M46" s="6">
+        <v>5640</v>
+      </c>
+      <c r="N46" s="6">
+        <v>32904.925620000002</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>